--- a/exports/report_final.xlsx
+++ b/exports/report_final.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,37 +417,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>sales</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>profit</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>new_cases</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>hospitalized</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>rolling_profit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sales_pct_change</t>
         </is>
@@ -581,7 +569,7 @@
         <v>1412.426666666667</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2751046753549648</v>
+        <v>0.2751046753549649</v>
       </c>
     </row>
     <row r="7">
@@ -606,7 +594,7 @@
         <v>1345.693333333333</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.038760539165786</v>
+        <v>-0.03876053916578603</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +619,7 @@
         <v>1496.94</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.0044555851817584</v>
+        <v>-0.004455585181758481</v>
       </c>
     </row>
     <row r="9">
@@ -656,7 +644,7 @@
         <v>1414.093333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0683249719034342</v>
+        <v>0.06832497190343423</v>
       </c>
     </row>
     <row r="10">
@@ -681,7 +669,7 @@
         <v>1598.7</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0697187107737816</v>
+        <v>-0.06971871077378167</v>
       </c>
     </row>
     <row r="11">
@@ -706,7 +694,7 @@
         <v>1574.87</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0135243730595793</v>
+        <v>0.01352437305957932</v>
       </c>
     </row>
     <row r="12">
@@ -756,7 +744,7 @@
         <v>1555.88</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0156722842854944</v>
+        <v>-0.0156722842854945</v>
       </c>
     </row>
     <row r="14">
@@ -781,7 +769,7 @@
         <v>1542.976666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0746022858078195</v>
+        <v>-0.07460228580781958</v>
       </c>
     </row>
     <row r="15">
@@ -806,7 +794,7 @@
         <v>1449.866666666667</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.0807790218039319</v>
+        <v>-0.08077902180393193</v>
       </c>
     </row>
     <row r="16">
@@ -831,7 +819,7 @@
         <v>1414.336666666667</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0109719501124604</v>
+        <v>-0.01097195011246044</v>
       </c>
     </row>
     <row r="17">
@@ -856,7 +844,7 @@
         <v>1299.576666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0444786048913903</v>
+        <v>0.04447860489139033</v>
       </c>
     </row>
     <row r="18">
@@ -875,13 +863,13 @@
         <v>15482</v>
       </c>
       <c r="E18" t="n">
-        <v>2562.290322580646</v>
+        <v>2562.290322580645</v>
       </c>
       <c r="F18" t="n">
         <v>1259.753333333333</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0206304137708068</v>
+        <v>0.02063041377080688</v>
       </c>
     </row>
     <row r="19">
@@ -906,7 +894,7 @@
         <v>1359.66</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0438153466796042</v>
+        <v>0.04381534667960429</v>
       </c>
     </row>
     <row r="20">
@@ -931,7 +919,7 @@
         <v>1460.583333333333</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0472335039348412</v>
+        <v>-0.04723350393484127</v>
       </c>
     </row>
     <row r="21">
@@ -956,7 +944,7 @@
         <v>1579.046666666666</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0250709140034445</v>
+        <v>-0.02507091400344452</v>
       </c>
     </row>
     <row r="22">
@@ -981,7 +969,7 @@
         <v>1336.15</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0316114874289381</v>
+        <v>0.03161148742893816</v>
       </c>
     </row>
     <row r="23">
@@ -1006,7 +994,7 @@
         <v>1450.453333333334</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0700233431928485</v>
+        <v>0.07002334319284853</v>
       </c>
     </row>
     <row r="24">
@@ -1031,7 +1019,7 @@
         <v>1517.216666666666</v>
       </c>
       <c r="G24" t="n">
-        <v>0.0704257490848063</v>
+        <v>0.07042574908480637</v>
       </c>
     </row>
     <row r="25">
@@ -1056,7 +1044,7 @@
         <v>1615.16</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.13932437016781</v>
+        <v>-0.1393243701678101</v>
       </c>
     </row>
     <row r="26">
@@ -1231,7 +1219,7 @@
         <v>1317.633333333333</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.1366383140789639</v>
+        <v>-0.136638314078964</v>
       </c>
     </row>
     <row r="33">
@@ -1256,7 +1244,7 @@
         <v>1201.97</v>
       </c>
       <c r="G33" t="n">
-        <v>-0.1098144628334296</v>
+        <v>-0.1098144628334297</v>
       </c>
     </row>
     <row r="34">
@@ -1281,7 +1269,7 @@
         <v>1299.053333333333</v>
       </c>
       <c r="G34" t="n">
-        <v>0.0973011580418898</v>
+        <v>0.09730115804188988</v>
       </c>
     </row>
     <row r="35">
@@ -1381,7 +1369,7 @@
         <v>1424.31</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0289242088693062</v>
+        <v>0.02892420886930624</v>
       </c>
     </row>
     <row r="39">
@@ -1456,7 +1444,7 @@
         <v>1276.506666666667</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.08542283072476591</v>
+        <v>-0.08542283072476597</v>
       </c>
     </row>
     <row r="42">
@@ -1606,7 +1594,7 @@
         <v>1741.716666666667</v>
       </c>
       <c r="G47" t="n">
-        <v>0.2468512759010985</v>
+        <v>0.2468512759010986</v>
       </c>
     </row>
     <row r="48">
@@ -1644,7 +1632,7 @@
         <v>29356.68</v>
       </c>
       <c r="C49" t="n">
-        <v>929.41</v>
+        <v>929.4100000000001</v>
       </c>
       <c r="D49" t="n">
         <v>15359</v>
@@ -1656,7 +1644,7 @@
         <v>1571.206666666667</v>
       </c>
       <c r="G49" t="n">
-        <v>-0.0665982433783298</v>
+        <v>-0.06659824337832987</v>
       </c>
     </row>
     <row r="50">
@@ -1706,7 +1694,7 @@
         <v>1112.06</v>
       </c>
       <c r="G51" t="n">
-        <v>-0.1985100808412818</v>
+        <v>-0.1985100808412819</v>
       </c>
     </row>
     <row r="52">
@@ -1728,10 +1716,10 @@
         <v>2367.548387096774</v>
       </c>
       <c r="F52" t="n">
-        <v>1236.353333333334</v>
+        <v>1236.353333333333</v>
       </c>
       <c r="G52" t="n">
-        <v>0.07635726305661419</v>
+        <v>0.07635726305661428</v>
       </c>
     </row>
     <row r="53">
@@ -1775,13 +1763,13 @@
         <v>15470</v>
       </c>
       <c r="E54" t="n">
-        <v>2805.709677419354</v>
+        <v>2805.709677419355</v>
       </c>
       <c r="F54" t="n">
         <v>1529.213333333333</v>
       </c>
       <c r="G54" t="n">
-        <v>0.0159162543768915</v>
+        <v>0.01591625437689159</v>
       </c>
     </row>
     <row r="55">
@@ -1831,7 +1819,7 @@
         <v>1565.996666666667</v>
       </c>
       <c r="G56" t="n">
-        <v>0.0064166556620588</v>
+        <v>0.006416655662058846</v>
       </c>
     </row>
     <row r="57">
@@ -1856,7 +1844,7 @@
         <v>1640.736666666667</v>
       </c>
       <c r="G57" t="n">
-        <v>0.07105066534682811</v>
+        <v>0.07105066534682813</v>
       </c>
     </row>
     <row r="58">
@@ -1881,7 +1869,7 @@
         <v>1760.283333333334</v>
       </c>
       <c r="G58" t="n">
-        <v>-0.0745321251280234</v>
+        <v>-0.07453212512802343</v>
       </c>
     </row>
     <row r="59">
@@ -1931,7 +1919,7 @@
         <v>1751.076666666667</v>
       </c>
       <c r="G60" t="n">
-        <v>-0.0027450474781328</v>
+        <v>-0.002745047478132867</v>
       </c>
     </row>
     <row r="61">
@@ -1956,7 +1944,7 @@
         <v>1779.423333333333</v>
       </c>
       <c r="G61" t="n">
-        <v>-0.0678846038497912</v>
+        <v>-0.06788460384979123</v>
       </c>
     </row>
     <row r="62">
@@ -2006,7 +1994,7 @@
         <v>1744.056666666667</v>
       </c>
       <c r="G63" t="n">
-        <v>-0.0838145614746971</v>
+        <v>-0.08381456147469712</v>
       </c>
     </row>
     <row r="64">
@@ -2031,7 +2019,7 @@
         <v>1919.976666666667</v>
       </c>
       <c r="G64" t="n">
-        <v>0.0275841080561576</v>
+        <v>0.02758410805615763</v>
       </c>
     </row>
     <row r="65">
@@ -2056,7 +2044,7 @@
         <v>1704.23</v>
       </c>
       <c r="G65" t="n">
-        <v>-0.1277950333983227</v>
+        <v>-0.1277950333983228</v>
       </c>
     </row>
     <row r="66">
@@ -2081,7 +2069,7 @@
         <v>1538.950000000001</v>
       </c>
       <c r="G66" t="n">
-        <v>0.2306192733006224</v>
+        <v>0.2306192733006225</v>
       </c>
     </row>
     <row r="67">
@@ -2156,7 +2144,7 @@
         <v>1685.393333333334</v>
       </c>
       <c r="G69" t="n">
-        <v>0.1438357930334641</v>
+        <v>0.1438357930334642</v>
       </c>
     </row>
     <row r="70">
@@ -2206,7 +2194,7 @@
         <v>1906.88</v>
       </c>
       <c r="G71" t="n">
-        <v>0.0381327434393732</v>
+        <v>0.03813274343937323</v>
       </c>
     </row>
     <row r="72">
@@ -2281,7 +2269,7 @@
         <v>1606.553333333334</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.0216893216267085</v>
+        <v>-0.02168932162670856</v>
       </c>
     </row>
     <row r="75">
@@ -2306,7 +2294,7 @@
         <v>1752.526666666667</v>
       </c>
       <c r="G75" t="n">
-        <v>-0.0583223587132061</v>
+        <v>-0.05832235871320612</v>
       </c>
     </row>
     <row r="76">
@@ -2331,7 +2319,7 @@
         <v>1879.226666666667</v>
       </c>
       <c r="G76" t="n">
-        <v>0.0198043436967905</v>
+        <v>0.01980434369679052</v>
       </c>
     </row>
     <row r="77">
@@ -2356,7 +2344,7 @@
         <v>1719.000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>-0.1065531367906152</v>
+        <v>-0.1065531367906153</v>
       </c>
     </row>
     <row r="78">
@@ -2381,7 +2369,7 @@
         <v>1736.453333333334</v>
       </c>
       <c r="G78" t="n">
-        <v>0.1035422322927683</v>
+        <v>0.1035422322927684</v>
       </c>
     </row>
     <row r="79">
@@ -2450,7 +2438,7 @@
         <v>15569</v>
       </c>
       <c r="E81" t="n">
-        <v>2738.290322580646</v>
+        <v>2738.290322580645</v>
       </c>
       <c r="F81" t="n">
         <v>1812.376666666667</v>
@@ -2481,7 +2469,7 @@
         <v>1618.086666666667</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.0367845006717949</v>
+        <v>-0.03678450067179495</v>
       </c>
     </row>
     <row r="83">
@@ -2506,7 +2494,7 @@
         <v>1707.496666666667</v>
       </c>
       <c r="G83" t="n">
-        <v>-0.2835664716324659</v>
+        <v>-0.283566471632466</v>
       </c>
     </row>
     <row r="84">
@@ -2531,7 +2519,7 @@
         <v>1598.353333333334</v>
       </c>
       <c r="G84" t="n">
-        <v>0.1251635238687287</v>
+        <v>0.1251635238687288</v>
       </c>
     </row>
     <row r="85">
@@ -2550,13 +2538,13 @@
         <v>15669</v>
       </c>
       <c r="E85" t="n">
-        <v>2621.709677419354</v>
+        <v>2621.709677419355</v>
       </c>
       <c r="F85" t="n">
         <v>1326.700000000001</v>
       </c>
       <c r="G85" t="n">
-        <v>-0.06425699972281999</v>
+        <v>-0.06425699972282006</v>
       </c>
     </row>
     <row r="86">
@@ -2631,7 +2619,7 @@
         <v>1476.74</v>
       </c>
       <c r="G88" t="n">
-        <v>0.1397469340821728</v>
+        <v>0.1397469340821729</v>
       </c>
     </row>
     <row r="89">
@@ -2656,7 +2644,7 @@
         <v>1799.26</v>
       </c>
       <c r="G89" t="n">
-        <v>-0.0725562655962457</v>
+        <v>-0.07255626559624573</v>
       </c>
     </row>
     <row r="90">
@@ -2681,7 +2669,7 @@
         <v>1894.156666666667</v>
       </c>
       <c r="G90" t="n">
-        <v>0.008495682966540999</v>
+        <v>0.008495682966541018</v>
       </c>
     </row>
     <row r="91">
@@ -2731,7 +2719,7 @@
         <v>1752.113333333334</v>
       </c>
       <c r="G92" t="n">
-        <v>0.1939116581740478</v>
+        <v>0.1939116581740479</v>
       </c>
     </row>
     <row r="93">
@@ -2756,7 +2744,7 @@
         <v>1834.373333333334</v>
       </c>
       <c r="G93" t="n">
-        <v>0.0378290054950642</v>
+        <v>0.03782900549506429</v>
       </c>
     </row>
     <row r="94">
@@ -2781,7 +2769,7 @@
         <v>2277.846666666667</v>
       </c>
       <c r="G94" t="n">
-        <v>-0.0246948053467065</v>
+        <v>-0.02469480534670654</v>
       </c>
     </row>
     <row r="95">
@@ -2806,7 +2794,7 @@
         <v>1926.556666666667</v>
       </c>
       <c r="G95" t="n">
-        <v>-0.0442771221510089</v>
+        <v>-0.04427712215100899</v>
       </c>
     </row>
     <row r="96">
@@ -2856,7 +2844,7 @@
         <v>1243.580000000001</v>
       </c>
       <c r="G97" t="n">
-        <v>0.0292113963265647</v>
+        <v>0.02921139632656478</v>
       </c>
     </row>
     <row r="98">
@@ -2875,7 +2863,7 @@
         <v>15535</v>
       </c>
       <c r="E98" t="n">
-        <v>2182.709677419354</v>
+        <v>2182.709677419355</v>
       </c>
       <c r="F98" t="n">
         <v>1364.063333333334</v>
@@ -2903,7 +2891,7 @@
         <v>2506</v>
       </c>
       <c r="F99" t="n">
-        <v>1388.593333333334</v>
+        <v>1388.593333333333</v>
       </c>
       <c r="G99" t="n">
         <v>-0.083722378820138</v>
@@ -2925,13 +2913,13 @@
         <v>15688</v>
       </c>
       <c r="E100" t="n">
-        <v>2255.290322580646</v>
+        <v>2255.290322580645</v>
       </c>
       <c r="F100" t="n">
         <v>1582.156666666667</v>
       </c>
       <c r="G100" t="n">
-        <v>-0.0095265884578398</v>
+        <v>-0.009526588457839824</v>
       </c>
     </row>
     <row r="101">
@@ -2981,7 +2969,7 @@
         <v>1522.703333333334</v>
       </c>
       <c r="G102" t="n">
-        <v>-0.0612097997701899</v>
+        <v>-0.06120979977018992</v>
       </c>
     </row>
     <row r="103">
@@ -3006,7 +2994,7 @@
         <v>1259.113333333334</v>
       </c>
       <c r="G103" t="n">
-        <v>-0.0372303641158682</v>
+        <v>-0.03723036411586822</v>
       </c>
     </row>
     <row r="104">
@@ -3025,13 +3013,13 @@
         <v>15341</v>
       </c>
       <c r="E104" t="n">
-        <v>2565.709677419354</v>
+        <v>2565.709677419355</v>
       </c>
       <c r="F104" t="n">
         <v>1062.303333333334</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0700669368035262</v>
+        <v>0.07006693680352627</v>
       </c>
     </row>
     <row r="105">
@@ -3056,7 +3044,7 @@
         <v>1211.276666666667</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0251082155160389</v>
+        <v>0.02510821551603892</v>
       </c>
     </row>
     <row r="106">
@@ -3081,7 +3069,7 @@
         <v>1425.426666666667</v>
       </c>
       <c r="G106" t="n">
-        <v>-0.0550641622668018</v>
+        <v>-0.05506416226680189</v>
       </c>
     </row>
     <row r="107">
@@ -3156,7 +3144,7 @@
         <v>1638.306666666667</v>
       </c>
       <c r="G109" t="n">
-        <v>0.0095435266470336</v>
+        <v>0.009543526647033618</v>
       </c>
     </row>
     <row r="110">
@@ -3181,7 +3169,7 @@
         <v>1736.116666666667</v>
       </c>
       <c r="G110" t="n">
-        <v>-0.038639367884955</v>
+        <v>-0.03863936788495503</v>
       </c>
     </row>
     <row r="111">
@@ -3231,7 +3219,7 @@
         <v>1328.333333333334</v>
       </c>
       <c r="G112" t="n">
-        <v>-0.0498334057656092</v>
+        <v>-0.04983340576560924</v>
       </c>
     </row>
     <row r="113">
@@ -3281,7 +3269,7 @@
         <v>1156.246666666667</v>
       </c>
       <c r="G114" t="n">
-        <v>-0.2382595854427238</v>
+        <v>-0.2382595854427239</v>
       </c>
     </row>
     <row r="115">
@@ -3306,7 +3294,7 @@
         <v>1291.846666666667</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0542470272960267</v>
+        <v>0.05424702729602671</v>
       </c>
     </row>
     <row r="116">
@@ -3331,7 +3319,7 @@
         <v>1281.120000000001</v>
       </c>
       <c r="G116" t="n">
-        <v>0.1167046046086128</v>
+        <v>0.1167046046086129</v>
       </c>
     </row>
     <row r="117">
@@ -3356,7 +3344,7 @@
         <v>1626.433333333334</v>
       </c>
       <c r="G117" t="n">
-        <v>0.2948783104830756</v>
+        <v>0.2948783104830757</v>
       </c>
     </row>
     <row r="118">
@@ -3378,7 +3366,7 @@
         <v>2263.833333333333</v>
       </c>
       <c r="F118" t="n">
-        <v>1838.573333333333</v>
+        <v>1838.573333333334</v>
       </c>
       <c r="G118" t="n">
         <v>-0.2254228844196244</v>
@@ -3403,10 +3391,10 @@
         <v>2430.16129032258</v>
       </c>
       <c r="F119" t="n">
-        <v>1840.65</v>
+        <v>1840.650000000001</v>
       </c>
       <c r="G119" t="n">
-        <v>0.0422587405087135</v>
+        <v>0.04225874050871359</v>
       </c>
     </row>
     <row r="120">
@@ -3428,10 +3416,10 @@
         <v>2531.6</v>
       </c>
       <c r="F120" t="n">
-        <v>1810.366666666668</v>
+        <v>1810.366666666667</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0124202071694645</v>
+        <v>0.01242020716946457</v>
       </c>
     </row>
     <row r="121">
@@ -3456,7 +3444,7 @@
         <v>1660.246666666667</v>
       </c>
       <c r="G121" t="n">
-        <v>0.0230123362515479</v>
+        <v>0.02301233625154797</v>
       </c>
     </row>
     <row r="122">
@@ -3481,7 +3469,7 @@
         <v>1519.036666666667</v>
       </c>
       <c r="G122" t="n">
-        <v>-0.1060034539102333</v>
+        <v>-0.1060034539102334</v>
       </c>
     </row>
     <row r="123">
@@ -3506,7 +3494,7 @@
         <v>1180.200000000001</v>
       </c>
       <c r="G123" t="n">
-        <v>-0.0465907892749567</v>
+        <v>-0.04659078927495675</v>
       </c>
     </row>
     <row r="124">
@@ -3556,7 +3544,7 @@
         <v>1442.330000000001</v>
       </c>
       <c r="G125" t="n">
-        <v>-0.0708237463575456</v>
+        <v>-0.07082374635754562</v>
       </c>
     </row>
     <row r="126">
@@ -3581,7 +3569,7 @@
         <v>1606.400000000001</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0589508985879332</v>
+        <v>0.05895089858793323</v>
       </c>
     </row>
     <row r="127">
@@ -3600,13 +3588,13 @@
         <v>15024</v>
       </c>
       <c r="E127" t="n">
-        <v>1949.566666666666</v>
+        <v>1949.566666666667</v>
       </c>
       <c r="F127" t="n">
         <v>1367.743333333334</v>
       </c>
       <c r="G127" t="n">
-        <v>-0.2259911609905289</v>
+        <v>-0.225991160990529</v>
       </c>
     </row>
     <row r="128">
@@ -3628,10 +3616,10 @@
         <v>2600.129032258064</v>
       </c>
       <c r="F128" t="n">
-        <v>1487.616666666668</v>
+        <v>1487.616666666667</v>
       </c>
       <c r="G128" t="n">
-        <v>0.1575017913147662</v>
+        <v>0.1575017913147663</v>
       </c>
     </row>
     <row r="129">
@@ -3656,7 +3644,7 @@
         <v>1521.166666666667</v>
       </c>
       <c r="G129" t="n">
-        <v>-0.0650764076626859</v>
+        <v>-0.06507640766268596</v>
       </c>
     </row>
     <row r="130">
@@ -3681,7 +3669,7 @@
         <v>1528.760000000001</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0904826789721353</v>
+        <v>0.09048267897213536</v>
       </c>
     </row>
     <row r="131">
@@ -3756,7 +3744,7 @@
         <v>1248.550000000001</v>
       </c>
       <c r="G133" t="n">
-        <v>0.0077639222790517</v>
+        <v>0.00776392227905176</v>
       </c>
     </row>
     <row r="134">
@@ -3781,7 +3769,7 @@
         <v>1447.556666666667</v>
       </c>
       <c r="G134" t="n">
-        <v>-0.0322407594950558</v>
+        <v>-0.03224075949505589</v>
       </c>
     </row>
     <row r="135">
@@ -3856,7 +3844,7 @@
         <v>1831.906666666667</v>
       </c>
       <c r="G137" t="n">
-        <v>0.0553096440130238</v>
+        <v>0.05530964401302385</v>
       </c>
     </row>
     <row r="138">
@@ -3881,7 +3869,7 @@
         <v>1804.383333333334</v>
       </c>
       <c r="G138" t="n">
-        <v>-0.0177099818714442</v>
+        <v>-0.01770998187144424</v>
       </c>
     </row>
     <row r="139">
@@ -3906,7 +3894,7 @@
         <v>1431.963333333334</v>
       </c>
       <c r="G139" t="n">
-        <v>-0.3469132334085448</v>
+        <v>-0.3469132334085449</v>
       </c>
     </row>
     <row r="140">
@@ -3956,7 +3944,7 @@
         <v>1291.206666666667</v>
       </c>
       <c r="G141" t="n">
-        <v>0.2034395569765394</v>
+        <v>0.2034395569765395</v>
       </c>
     </row>
     <row r="142">
@@ -3981,7 +3969,7 @@
         <v>1632.806666666667</v>
       </c>
       <c r="G142" t="n">
-        <v>-0.0544976924192839</v>
+        <v>-0.05449769241928393</v>
       </c>
     </row>
     <row r="143">
@@ -4006,7 +3994,7 @@
         <v>1594.533333333334</v>
       </c>
       <c r="G143" t="n">
-        <v>-0.0463627028364185</v>
+        <v>-0.04636270283641852</v>
       </c>
     </row>
     <row r="144">
@@ -4031,7 +4019,7 @@
         <v>1513.530000000001</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0504069458083915</v>
+        <v>0.05040694580839156</v>
       </c>
     </row>
     <row r="145">
@@ -4056,7 +4044,7 @@
         <v>1284.263333333334</v>
       </c>
       <c r="G145" t="n">
-        <v>-0.0082240786406629</v>
+        <v>-0.008224078640662991</v>
       </c>
     </row>
     <row r="146">
@@ -4125,13 +4113,13 @@
         <v>15492</v>
       </c>
       <c r="E148" t="n">
-        <v>2841.290322580646</v>
+        <v>2841.290322580645</v>
       </c>
       <c r="F148" t="n">
         <v>1259.213333333334</v>
       </c>
       <c r="G148" t="n">
-        <v>0.0501787201236754</v>
+        <v>0.05017872012367541</v>
       </c>
     </row>
     <row r="149">
@@ -4206,7 +4194,7 @@
         <v>1274.320000000001</v>
       </c>
       <c r="G151" t="n">
-        <v>0.0562516119356342</v>
+        <v>0.05625161193563422</v>
       </c>
     </row>
     <row r="152">
@@ -4225,13 +4213,13 @@
         <v>15429</v>
       </c>
       <c r="E152" t="n">
-        <v>2986.290322580646</v>
+        <v>2986.290322580645</v>
       </c>
       <c r="F152" t="n">
         <v>1345.856666666667</v>
       </c>
       <c r="G152" t="n">
-        <v>-0.111951925547573</v>
+        <v>-0.1119519255475731</v>
       </c>
     </row>
     <row r="153">
@@ -4250,13 +4238,13 @@
         <v>15566</v>
       </c>
       <c r="E153" t="n">
-        <v>2845.290322580646</v>
+        <v>2845.290322580645</v>
       </c>
       <c r="F153" t="n">
         <v>1455.923333333334</v>
       </c>
       <c r="G153" t="n">
-        <v>0.1150879810273399</v>
+        <v>0.11508798102734</v>
       </c>
     </row>
     <row r="154">
@@ -4281,7 +4269,7 @@
         <v>1643.286666666668</v>
       </c>
       <c r="G154" t="n">
-        <v>-0.0666760058410836</v>
+        <v>-0.06667600584108369</v>
       </c>
     </row>
     <row r="155">
@@ -4306,7 +4294,7 @@
         <v>1713.540000000001</v>
       </c>
       <c r="G155" t="n">
-        <v>0.2209902116601931</v>
+        <v>0.2209902116601932</v>
       </c>
     </row>
     <row r="156">
@@ -4353,10 +4341,10 @@
         <v>2300.83870967742</v>
       </c>
       <c r="F157" t="n">
-        <v>1338.16</v>
+        <v>1338.160000000001</v>
       </c>
       <c r="G157" t="n">
-        <v>0.0681744301143607</v>
+        <v>0.06817443011436075</v>
       </c>
     </row>
     <row r="158">
@@ -4406,7 +4394,7 @@
         <v>1327.096666666667</v>
       </c>
       <c r="G159" t="n">
-        <v>-0.2346612822507575</v>
+        <v>-0.2346612822507576</v>
       </c>
     </row>
     <row r="160">
@@ -4431,7 +4419,7 @@
         <v>1252.996666666667</v>
       </c>
       <c r="G160" t="n">
-        <v>-0.0292079068592708</v>
+        <v>-0.02920790685927088</v>
       </c>
     </row>
     <row r="161">
@@ -4481,7 +4469,7 @@
         <v>1420.953333333334</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0560809965144832</v>
+        <v>0.05608099651448328</v>
       </c>
     </row>
     <row r="163">
@@ -4506,7 +4494,7 @@
         <v>1851.076666666667</v>
       </c>
       <c r="G163" t="n">
-        <v>0.0038533779928673</v>
+        <v>0.003853377992867335</v>
       </c>
     </row>
     <row r="164">
@@ -4525,7 +4513,7 @@
         <v>15520</v>
       </c>
       <c r="E164" t="n">
-        <v>2432.290322580646</v>
+        <v>2432.290322580645</v>
       </c>
       <c r="F164" t="n">
         <v>1871.106666666667</v>
@@ -4556,7 +4544,7 @@
         <v>1804.860000000001</v>
       </c>
       <c r="G165" t="n">
-        <v>-0.0519190799122737</v>
+        <v>-0.05191907991227374</v>
       </c>
     </row>
     <row r="166">
@@ -4581,7 +4569,7 @@
         <v>1544.000000000001</v>
       </c>
       <c r="G166" t="n">
-        <v>-0.2031599743496229</v>
+        <v>-0.203159974349623</v>
       </c>
     </row>
     <row r="167">
@@ -4631,7 +4619,7 @@
         <v>1217.253333333334</v>
       </c>
       <c r="G168" t="n">
-        <v>0.09352219106145999</v>
+        <v>0.09352219106146009</v>
       </c>
     </row>
     <row r="169">
@@ -4653,10 +4641,10 @@
         <v>2775.741935483871</v>
       </c>
       <c r="F169" t="n">
-        <v>1095.41</v>
+        <v>1095.410000000001</v>
       </c>
       <c r="G169" t="n">
-        <v>-0.0020073396893431</v>
+        <v>-0.002007339689343191</v>
       </c>
     </row>
     <row r="170">
@@ -4681,7 +4669,7 @@
         <v>1212.460000000001</v>
       </c>
       <c r="G170" t="n">
-        <v>-0.1012987498905164</v>
+        <v>-0.1012987498905165</v>
       </c>
     </row>
     <row r="171">
@@ -4706,7 +4694,7 @@
         <v>1326.926666666667</v>
       </c>
       <c r="G171" t="n">
-        <v>-0.0431063195225065</v>
+        <v>-0.04310631952250654</v>
       </c>
     </row>
     <row r="172">
@@ -4731,7 +4719,7 @@
         <v>1358.920000000001</v>
       </c>
       <c r="G172" t="n">
-        <v>-0.0449980800195128</v>
+        <v>-0.04499808001951289</v>
       </c>
     </row>
     <row r="173">
@@ -4831,7 +4819,7 @@
         <v>1320.843333333334</v>
       </c>
       <c r="G176" t="n">
-        <v>0.022034042581055</v>
+        <v>0.02203404258105501</v>
       </c>
     </row>
     <row r="177">
@@ -4856,7 +4844,7 @@
         <v>1357.566666666667</v>
       </c>
       <c r="G177" t="n">
-        <v>0.08124326691356119</v>
+        <v>0.08124326691356121</v>
       </c>
     </row>
     <row r="178">
@@ -4881,7 +4869,7 @@
         <v>1426.306666666667</v>
       </c>
       <c r="G178" t="n">
-        <v>0.0331069949033115</v>
+        <v>0.03310699490331159</v>
       </c>
     </row>
     <row r="179">
@@ -4956,7 +4944,7 @@
         <v>1843.700000000001</v>
       </c>
       <c r="G181" t="n">
-        <v>-0.0980062847874968</v>
+        <v>-0.09800628478749684</v>
       </c>
     </row>
     <row r="182">
@@ -4981,7 +4969,7 @@
         <v>1857.526666666667</v>
       </c>
       <c r="G182" t="n">
-        <v>-0.1085808212771379</v>
+        <v>-0.108580821277138</v>
       </c>
     </row>
     <row r="183">
@@ -5006,7 +4994,7 @@
         <v>1449.166666666667</v>
       </c>
       <c r="G183" t="n">
-        <v>0.0289510044252014</v>
+        <v>0.02895100442520149</v>
       </c>
     </row>
     <row r="184">
@@ -5031,7 +5019,7 @@
         <v>1482.186666666667</v>
       </c>
       <c r="G184" t="n">
-        <v>-0.1220985025547348</v>
+        <v>-0.1220985025547349</v>
       </c>
     </row>
     <row r="185">
@@ -5106,7 +5094,7 @@
         <v>1442.390000000001</v>
       </c>
       <c r="G187" t="n">
-        <v>0.0901354347390865</v>
+        <v>0.09013543473908658</v>
       </c>
     </row>
     <row r="188">
@@ -5131,7 +5119,7 @@
         <v>1415.120000000001</v>
       </c>
       <c r="G188" t="n">
-        <v>-0.0209450609956374</v>
+        <v>-0.02094506099563742</v>
       </c>
     </row>
     <row r="189">
@@ -5156,7 +5144,7 @@
         <v>1253.923333333334</v>
       </c>
       <c r="G189" t="n">
-        <v>-0.2320616281728392</v>
+        <v>-0.2320616281728393</v>
       </c>
     </row>
     <row r="190">
@@ -5231,7 +5219,7 @@
         <v>1501.906666666667</v>
       </c>
       <c r="G192" t="n">
-        <v>0.0572342852807992</v>
+        <v>0.05723428528079921</v>
       </c>
     </row>
     <row r="193">
@@ -5256,7 +5244,7 @@
         <v>1252.646666666667</v>
       </c>
       <c r="G193" t="n">
-        <v>0.0293978442247839</v>
+        <v>0.02939784422478398</v>
       </c>
     </row>
     <row r="194">
@@ -5356,7 +5344,7 @@
         <v>1432.740000000001</v>
       </c>
       <c r="G197" t="n">
-        <v>0.0108657968204923</v>
+        <v>0.01086579682049238</v>
       </c>
     </row>
     <row r="198">
@@ -5456,7 +5444,7 @@
         <v>1595.796666666667</v>
       </c>
       <c r="G201" t="n">
-        <v>0.0553922029285136</v>
+        <v>0.05539220292851366</v>
       </c>
     </row>
     <row r="202">
@@ -5481,7 +5469,7 @@
         <v>1382.203333333334</v>
       </c>
       <c r="G202" t="n">
-        <v>-0.0794504727302468</v>
+        <v>-0.07945047273024686</v>
       </c>
     </row>
     <row r="203">
@@ -5506,7 +5494,7 @@
         <v>1328.853333333334</v>
       </c>
       <c r="G203" t="n">
-        <v>-0.0201844045364217</v>
+        <v>-0.02018440453642179</v>
       </c>
     </row>
     <row r="204">
@@ -5528,7 +5516,7 @@
         <v>2574.5</v>
       </c>
       <c r="F204" t="n">
-        <v>1581.616666666668</v>
+        <v>1581.616666666667</v>
       </c>
       <c r="G204" t="n">
         <v>0.1712359795409248</v>
@@ -5606,7 +5594,7 @@
         <v>1201.803333333334</v>
       </c>
       <c r="G207" t="n">
-        <v>-0.1979977738248671</v>
+        <v>-0.1979977738248672</v>
       </c>
     </row>
     <row r="208">
@@ -5656,7 +5644,7 @@
         <v>1255.976666666667</v>
       </c>
       <c r="G209" t="n">
-        <v>-0.0237050659264399</v>
+        <v>-0.02370506592643995</v>
       </c>
     </row>
     <row r="210">
@@ -5681,7 +5669,7 @@
         <v>1199.526666666667</v>
       </c>
       <c r="G210" t="n">
-        <v>-0.0274099916053057</v>
+        <v>-0.02740999160530577</v>
       </c>
     </row>
     <row r="211">
@@ -5706,7 +5694,7 @@
         <v>1087.690000000001</v>
       </c>
       <c r="G211" t="n">
-        <v>0.1202374953362963</v>
+        <v>0.1202374953362964</v>
       </c>
     </row>
     <row r="212">
@@ -5725,13 +5713,13 @@
         <v>15439</v>
       </c>
       <c r="E212" t="n">
-        <v>2518.709677419354</v>
+        <v>2518.709677419355</v>
       </c>
       <c r="F212" t="n">
         <v>1134.836666666667</v>
       </c>
       <c r="G212" t="n">
-        <v>0.0059045614621104</v>
+        <v>0.005904561462110491</v>
       </c>
     </row>
     <row r="213">
@@ -5756,7 +5744,7 @@
         <v>1013.110000000001</v>
       </c>
       <c r="G213" t="n">
-        <v>-0.0880722068348479</v>
+        <v>-0.08807220683484795</v>
       </c>
     </row>
     <row r="214">
@@ -5781,7 +5769,7 @@
         <v>902.0266666666672</v>
       </c>
       <c r="G214" t="n">
-        <v>-0.0414361605471196</v>
+        <v>-0.04143616054711963</v>
       </c>
     </row>
     <row r="215">
@@ -5803,10 +5791,10 @@
         <v>2323.41935483871</v>
       </c>
       <c r="F215" t="n">
-        <v>920.7066666666672</v>
+        <v>920.7066666666673</v>
       </c>
       <c r="G215" t="n">
-        <v>0.1098573742407031</v>
+        <v>0.1098573742407032</v>
       </c>
     </row>
     <row r="216">
@@ -5831,7 +5819,7 @@
         <v>1080.310000000001</v>
       </c>
       <c r="G216" t="n">
-        <v>0.0335265780575428</v>
+        <v>0.03352657805754289</v>
       </c>
     </row>
     <row r="217">
@@ -5850,13 +5838,13 @@
         <v>15583</v>
       </c>
       <c r="E217" t="n">
-        <v>2384.709677419354</v>
+        <v>2384.709677419355</v>
       </c>
       <c r="F217" t="n">
         <v>1538.503333333334</v>
       </c>
       <c r="G217" t="n">
-        <v>0.0975065475039278</v>
+        <v>0.09750654750392784</v>
       </c>
     </row>
     <row r="218">
@@ -5881,7 +5869,7 @@
         <v>1805.553333333334</v>
       </c>
       <c r="G218" t="n">
-        <v>0.07546286882902969</v>
+        <v>0.07546286882902975</v>
       </c>
     </row>
     <row r="219">
@@ -6006,7 +5994,7 @@
         <v>1800.946666666667</v>
       </c>
       <c r="G223" t="n">
-        <v>0.0825964331075852</v>
+        <v>0.08259643310758524</v>
       </c>
     </row>
     <row r="224">
@@ -6031,7 +6019,7 @@
         <v>1770.353333333334</v>
       </c>
       <c r="G224" t="n">
-        <v>0.2900928338152448</v>
+        <v>0.2900928338152449</v>
       </c>
     </row>
     <row r="225">
@@ -6106,7 +6094,7 @@
         <v>1324.966666666667</v>
       </c>
       <c r="G227" t="n">
-        <v>0.0680320815478736</v>
+        <v>0.06803208154787366</v>
       </c>
     </row>
     <row r="228">
@@ -6131,7 +6119,7 @@
         <v>1437.373333333334</v>
       </c>
       <c r="G228" t="n">
-        <v>0.0475548283388755</v>
+        <v>0.04755482833887559</v>
       </c>
     </row>
     <row r="229">
@@ -6156,7 +6144,7 @@
         <v>1404.333333333334</v>
       </c>
       <c r="G229" t="n">
-        <v>-0.07921870856019581</v>
+        <v>-0.07921870856019586</v>
       </c>
     </row>
     <row r="230">
@@ -6181,7 +6169,7 @@
         <v>1398.360000000001</v>
       </c>
       <c r="G230" t="n">
-        <v>0.1439443074314363</v>
+        <v>0.1439443074314364</v>
       </c>
     </row>
     <row r="231">
@@ -6231,7 +6219,7 @@
         <v>1337.700000000001</v>
       </c>
       <c r="G232" t="n">
-        <v>-0.0029508394977123</v>
+        <v>-0.002950839497712354</v>
       </c>
     </row>
     <row r="233">
@@ -6256,7 +6244,7 @@
         <v>1268.736666666667</v>
       </c>
       <c r="G233" t="n">
-        <v>0.0116276804587704</v>
+        <v>0.0116276804587705</v>
       </c>
     </row>
     <row r="234">
@@ -6281,7 +6269,7 @@
         <v>1269.783333333334</v>
       </c>
       <c r="G234" t="n">
-        <v>0.2000996985064844</v>
+        <v>0.2000996985064845</v>
       </c>
     </row>
     <row r="235">
@@ -6431,7 +6419,7 @@
         <v>1592.786666666667</v>
       </c>
       <c r="G240" t="n">
-        <v>0.0008963310822935</v>
+        <v>0.0008963310822935888</v>
       </c>
     </row>
     <row r="241">
@@ -6456,7 +6444,7 @@
         <v>1390.766666666667</v>
       </c>
       <c r="G241" t="n">
-        <v>-0.0802596915732586</v>
+        <v>-0.08025969157325863</v>
       </c>
     </row>
     <row r="242">
@@ -6531,7 +6519,7 @@
         <v>1701.356666666667</v>
       </c>
       <c r="G244" t="n">
-        <v>-0.0106235869780748</v>
+        <v>-0.01062358697807486</v>
       </c>
     </row>
     <row r="245">
@@ -6606,7 +6594,7 @@
         <v>1816.263333333334</v>
       </c>
       <c r="G247" t="n">
-        <v>-0.0380214271865212</v>
+        <v>-0.03802142718652124</v>
       </c>
     </row>
     <row r="248">
@@ -6631,7 +6619,7 @@
         <v>1842.213333333334</v>
       </c>
       <c r="G248" t="n">
-        <v>-0.0800154583512078</v>
+        <v>-0.08001545835120782</v>
       </c>
     </row>
     <row r="249">
@@ -6656,7 +6644,7 @@
         <v>1598.506666666667</v>
       </c>
       <c r="G249" t="n">
-        <v>-0.0154082962337657</v>
+        <v>-0.01540829623376572</v>
       </c>
     </row>
     <row r="250">
@@ -6681,7 +6669,7 @@
         <v>1653.526666666667</v>
       </c>
       <c r="G250" t="n">
-        <v>-0.08842060782937471</v>
+        <v>-0.08842060782937478</v>
       </c>
     </row>
     <row r="251">
@@ -6731,7 +6719,7 @@
         <v>1611.590000000001</v>
       </c>
       <c r="G252" t="n">
-        <v>-0.1149489431707254</v>
+        <v>-0.1149489431707255</v>
       </c>
     </row>
     <row r="253">
@@ -6756,7 +6744,7 @@
         <v>1462.623333333334</v>
       </c>
       <c r="G253" t="n">
-        <v>-0.07267001161948421</v>
+        <v>-0.07267001161948428</v>
       </c>
     </row>
     <row r="254">
@@ -6806,7 +6794,7 @@
         <v>1347.976666666667</v>
       </c>
       <c r="G255" t="n">
-        <v>-0.0983759916063953</v>
+        <v>-0.09837599160639532</v>
       </c>
     </row>
     <row r="256">
@@ -6831,7 +6819,7 @@
         <v>1354.246666666667</v>
       </c>
       <c r="G256" t="n">
-        <v>-0.0745608896472921</v>
+        <v>-0.07456088964729213</v>
       </c>
     </row>
     <row r="257">
@@ -6856,7 +6844,7 @@
         <v>1306.090000000001</v>
       </c>
       <c r="G257" t="n">
-        <v>0.1885529194661361</v>
+        <v>0.1885529194661362</v>
       </c>
     </row>
     <row r="258">
@@ -6881,7 +6869,7 @@
         <v>1367.353333333334</v>
       </c>
       <c r="G258" t="n">
-        <v>-0.188607119461681</v>
+        <v>-0.1886071194616811</v>
       </c>
     </row>
     <row r="259">
@@ -6931,7 +6919,7 @@
         <v>1559.453333333334</v>
       </c>
       <c r="G260" t="n">
-        <v>0.046845831366963</v>
+        <v>0.04684583136696308</v>
       </c>
     </row>
     <row r="261">
@@ -6956,7 +6944,7 @@
         <v>1657.876666666667</v>
       </c>
       <c r="G261" t="n">
-        <v>0.0296275310887781</v>
+        <v>0.02962753108877814</v>
       </c>
     </row>
     <row r="262">
@@ -6981,7 +6969,7 @@
         <v>1644.736666666667</v>
       </c>
       <c r="G262" t="n">
-        <v>-0.0117282716236156</v>
+        <v>-0.01172827162361567</v>
       </c>
     </row>
     <row r="263">
@@ -7000,13 +6988,13 @@
         <v>15619</v>
       </c>
       <c r="E263" t="n">
-        <v>2561.709677419354</v>
+        <v>2561.709677419355</v>
       </c>
       <c r="F263" t="n">
         <v>1580.696666666667</v>
       </c>
       <c r="G263" t="n">
-        <v>-0.042866758931692</v>
+        <v>-0.04286675893169201</v>
       </c>
     </row>
     <row r="264">
@@ -7031,7 +7019,7 @@
         <v>1495.59</v>
       </c>
       <c r="G264" t="n">
-        <v>-0.0333081970790911</v>
+        <v>-0.03330819707909116</v>
       </c>
     </row>
     <row r="265">
@@ -7056,7 +7044,7 @@
         <v>1446.693333333334</v>
       </c>
       <c r="G265" t="n">
-        <v>0.1257702563045015</v>
+        <v>0.1257702563045016</v>
       </c>
     </row>
     <row r="266">
@@ -7206,7 +7194,7 @@
         <v>1191.093333333334</v>
       </c>
       <c r="G271" t="n">
-        <v>0.0576397106441703</v>
+        <v>0.05763971064417039</v>
       </c>
     </row>
     <row r="272">
@@ -7231,7 +7219,7 @@
         <v>1286.916666666667</v>
       </c>
       <c r="G272" t="n">
-        <v>0.009240914295674999</v>
+        <v>0.009240914295675084</v>
       </c>
     </row>
     <row r="273">
@@ -7256,7 +7244,7 @@
         <v>1715.233333333334</v>
       </c>
       <c r="G273" t="n">
-        <v>0.0801000393937185</v>
+        <v>0.08010003939371857</v>
       </c>
     </row>
     <row r="274">
@@ -7306,7 +7294,7 @@
         <v>1847.236666666667</v>
       </c>
       <c r="G275" t="n">
-        <v>0.069849465607618</v>
+        <v>0.06984946560761807</v>
       </c>
     </row>
     <row r="276">
@@ -7331,7 +7319,7 @@
         <v>1571.703333333334</v>
       </c>
       <c r="G276" t="n">
-        <v>-0.0336350212394941</v>
+        <v>-0.03363502123949413</v>
       </c>
     </row>
     <row r="277">
@@ -7356,7 +7344,7 @@
         <v>1660.410000000001</v>
       </c>
       <c r="G277" t="n">
-        <v>0.0699644208546288</v>
+        <v>0.06996442085462884</v>
       </c>
     </row>
     <row r="278">
@@ -7406,7 +7394,7 @@
         <v>1410.873333333334</v>
       </c>
       <c r="G279" t="n">
-        <v>0.1331203443842878</v>
+        <v>0.1331203443842879</v>
       </c>
     </row>
     <row r="280">
@@ -7425,7 +7413,7 @@
         <v>15387</v>
       </c>
       <c r="E280" t="n">
-        <v>2505.290322580646</v>
+        <v>2505.290322580645</v>
       </c>
       <c r="F280" t="n">
         <v>1525.456666666667</v>
@@ -7456,7 +7444,7 @@
         <v>1566.813333333334</v>
       </c>
       <c r="G281" t="n">
-        <v>0.0853314331260199</v>
+        <v>0.08533143312601998</v>
       </c>
     </row>
     <row r="282">
@@ -7481,7 +7469,7 @@
         <v>1835.013333333334</v>
       </c>
       <c r="G282" t="n">
-        <v>0.1380135101600907</v>
+        <v>0.1380135101600908</v>
       </c>
     </row>
     <row r="283">
@@ -7506,7 +7494,7 @@
         <v>1850.920000000001</v>
       </c>
       <c r="G283" t="n">
-        <v>-0.1383111774852274</v>
+        <v>-0.1383111774852275</v>
       </c>
     </row>
     <row r="284">
@@ -7531,7 +7519,7 @@
         <v>1816.243333333334</v>
       </c>
       <c r="G284" t="n">
-        <v>-0.1840499868178879</v>
+        <v>-0.184049986817888</v>
       </c>
     </row>
     <row r="285">
@@ -7550,7 +7538,7 @@
         <v>15458</v>
       </c>
       <c r="E285" t="n">
-        <v>2745.290322580646</v>
+        <v>2745.290322580645</v>
       </c>
       <c r="F285" t="n">
         <v>1500.080000000001</v>
@@ -7575,7 +7563,7 @@
         <v>14774</v>
       </c>
       <c r="E286" t="n">
-        <v>1894.933333333334</v>
+        <v>1894.933333333333</v>
       </c>
       <c r="F286" t="n">
         <v>1311.113333333334</v>
@@ -7631,7 +7619,7 @@
         <v>1583.700000000001</v>
       </c>
       <c r="G288" t="n">
-        <v>0.0681419663548166</v>
+        <v>0.06814196635481662</v>
       </c>
     </row>
     <row r="289">
@@ -7681,7 +7669,7 @@
         <v>1761.666666666667</v>
       </c>
       <c r="G290" t="n">
-        <v>0.0386276568134893</v>
+        <v>0.03862765681348934</v>
       </c>
     </row>
     <row r="291">
@@ -7731,7 +7719,7 @@
         <v>1291.24</v>
       </c>
       <c r="G292" t="n">
-        <v>0.2924450688801709</v>
+        <v>0.292445068880171</v>
       </c>
     </row>
     <row r="293">
@@ -7781,7 +7769,7 @@
         <v>1528.27</v>
       </c>
       <c r="G294" t="n">
-        <v>-0.0398266770978049</v>
+        <v>-0.03982667709780496</v>
       </c>
     </row>
     <row r="295">
@@ -7806,7 +7794,7 @@
         <v>1496.183333333334</v>
       </c>
       <c r="G295" t="n">
-        <v>-0.1295356345571325</v>
+        <v>-0.1295356345571326</v>
       </c>
     </row>
     <row r="296">
@@ -7856,7 +7844,7 @@
         <v>1750.940000000001</v>
       </c>
       <c r="G297" t="n">
-        <v>-0.0651567937825845</v>
+        <v>-0.06515679378258454</v>
       </c>
     </row>
     <row r="298">
@@ -7956,7 +7944,7 @@
         <v>1554.923333333334</v>
       </c>
       <c r="G301" t="n">
-        <v>-0.0256723211610371</v>
+        <v>-0.02567232116103713</v>
       </c>
     </row>
     <row r="302">
@@ -7981,7 +7969,7 @@
         <v>1307.120000000001</v>
       </c>
       <c r="G302" t="n">
-        <v>0.0835119179993126</v>
+        <v>0.08351191799931268</v>
       </c>
     </row>
     <row r="303">
@@ -8006,7 +7994,7 @@
         <v>1181.096666666667</v>
       </c>
       <c r="G303" t="n">
-        <v>-0.0141071989235255</v>
+        <v>-0.01410719892352552</v>
       </c>
     </row>
     <row r="304">
@@ -8056,7 +8044,7 @@
         <v>1147.696666666667</v>
       </c>
       <c r="G305" t="n">
-        <v>-0.0677954326141977</v>
+        <v>-0.06779543261419774</v>
       </c>
     </row>
     <row r="306">
@@ -8081,7 +8069,7 @@
         <v>1188.170000000001</v>
       </c>
       <c r="G306" t="n">
-        <v>0.1272022580141991</v>
+        <v>0.1272022580141992</v>
       </c>
     </row>
     <row r="307">
@@ -8131,7 +8119,7 @@
         <v>1284.690000000001</v>
       </c>
       <c r="G308" t="n">
-        <v>0.0513094697556761</v>
+        <v>0.05130946975567618</v>
       </c>
     </row>
     <row r="309">
@@ -8150,13 +8138,13 @@
         <v>15466</v>
       </c>
       <c r="E309" t="n">
-        <v>2407.709677419354</v>
+        <v>2407.709677419355</v>
       </c>
       <c r="F309" t="n">
         <v>1361.676666666667</v>
       </c>
       <c r="G309" t="n">
-        <v>0.2981882012691554</v>
+        <v>0.2981882012691555</v>
       </c>
     </row>
     <row r="310">
@@ -8181,7 +8169,7 @@
         <v>1459.266666666667</v>
       </c>
       <c r="G310" t="n">
-        <v>-0.2158579951215211</v>
+        <v>-0.2158579951215212</v>
       </c>
     </row>
     <row r="311">
@@ -8200,7 +8188,7 @@
         <v>15483</v>
       </c>
       <c r="E311" t="n">
-        <v>2264.290322580646</v>
+        <v>2264.290322580645</v>
       </c>
       <c r="F311" t="n">
         <v>1621.943333333334</v>
@@ -8231,7 +8219,7 @@
         <v>1702.813333333334</v>
       </c>
       <c r="G312" t="n">
-        <v>0.0436036408145994</v>
+        <v>0.04360364081459944</v>
       </c>
     </row>
     <row r="313">
@@ -8256,7 +8244,7 @@
         <v>1657.233333333334</v>
       </c>
       <c r="G313" t="n">
-        <v>-0.0145263739631775</v>
+        <v>-0.01452637396317757</v>
       </c>
     </row>
     <row r="314">
@@ -8275,13 +8263,13 @@
         <v>15584</v>
       </c>
       <c r="E314" t="n">
-        <v>2151.290322580646</v>
+        <v>2151.290322580645</v>
       </c>
       <c r="F314" t="n">
         <v>1628.130000000001</v>
       </c>
       <c r="G314" t="n">
-        <v>-0.0826675915319724</v>
+        <v>-0.08266759153197245</v>
       </c>
     </row>
     <row r="315">
@@ -8306,7 +8294,7 @@
         <v>1542.590000000001</v>
       </c>
       <c r="G315" t="n">
-        <v>0.0934219856676872</v>
+        <v>0.09342198566768722</v>
       </c>
     </row>
     <row r="316">
@@ -8331,7 +8319,7 @@
         <v>1795.396666666667</v>
       </c>
       <c r="G316" t="n">
-        <v>0.0900345928888495</v>
+        <v>0.09003459288884952</v>
       </c>
     </row>
     <row r="317">
@@ -8356,7 +8344,7 @@
         <v>1636.940000000001</v>
       </c>
       <c r="G317" t="n">
-        <v>-0.1383778032869501</v>
+        <v>-0.1383778032869502</v>
       </c>
     </row>
     <row r="318">
@@ -8381,7 +8369,7 @@
         <v>1533.873333333334</v>
       </c>
       <c r="G318" t="n">
-        <v>0.0584258556418026</v>
+        <v>0.05842585564180269</v>
       </c>
     </row>
     <row r="319">
@@ -8431,7 +8419,7 @@
         <v>1541.863333333334</v>
       </c>
       <c r="G320" t="n">
-        <v>0.3229700088670912</v>
+        <v>0.3229700088670913</v>
       </c>
     </row>
     <row r="321">
@@ -8456,7 +8444,7 @@
         <v>1865.63</v>
       </c>
       <c r="G321" t="n">
-        <v>-0.0036731788036995</v>
+        <v>-0.003673178803699551</v>
       </c>
     </row>
     <row r="322">
@@ -8481,7 +8469,7 @@
         <v>1692.773333333334</v>
       </c>
       <c r="G322" t="n">
-        <v>-0.1012979162656678</v>
+        <v>-0.1012979162656679</v>
       </c>
     </row>
     <row r="323">
@@ -8503,10 +8491,10 @@
         <v>2775.903225806452</v>
       </c>
       <c r="F323" t="n">
-        <v>1876.573333333333</v>
+        <v>1876.573333333334</v>
       </c>
       <c r="G323" t="n">
-        <v>0.0616802125703455</v>
+        <v>0.06168021257034551</v>
       </c>
     </row>
     <row r="324">
@@ -8556,7 +8544,7 @@
         <v>1970.653333333334</v>
       </c>
       <c r="G325" t="n">
-        <v>0.0411939837561976</v>
+        <v>0.04119398375619765</v>
       </c>
     </row>
     <row r="326">
@@ -8581,7 +8569,7 @@
         <v>1690.163333333334</v>
       </c>
       <c r="G326" t="n">
-        <v>0.0552203354229461</v>
+        <v>0.05522033542294613</v>
       </c>
     </row>
     <row r="327">
@@ -8656,7 +8644,7 @@
         <v>1645.700000000001</v>
       </c>
       <c r="G329" t="n">
-        <v>-0.1557905876472954</v>
+        <v>-0.1557905876472955</v>
       </c>
     </row>
     <row r="330">
@@ -8681,7 +8669,7 @@
         <v>1362.466666666667</v>
       </c>
       <c r="G330" t="n">
-        <v>-0.4179233980225065</v>
+        <v>-0.4179233980225066</v>
       </c>
     </row>
   </sheetData>
